--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T09:29:21+00:00</t>
+    <t>2025-12-23T09:35:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T09:35:21+00:00</t>
+    <t>2025-12-23T09:39:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T09:39:52+00:00</t>
+    <t>2025-12-23T09:57:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T09:57:47+00:00</t>
+    <t>2025-12-23T10:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T10:01:19+00:00</t>
+    <t>2026-01-06T09:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:35:23+00:00</t>
+    <t>2026-03-24T16:04:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,7 +66,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -111,7 +111,7 @@
     <t>Supplements</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/v3-AdministrativeGender|3.0.0</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-AdministrativeGender|4.0.0</t>
   </si>
   <si>
     <t>Count</t>

--- a/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-v3-AdministrativeGender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T16:04:23+00:00</t>
+    <t>2026-03-24T16:44:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
